--- a/StructureDefinition-SEEHDSLMMedicationHistory.xlsx
+++ b/StructureDefinition-SEEHDSLMMedicationHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMMedicationHistory.xlsx
+++ b/StructureDefinition-SEEHDSLMMedicationHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMMedicationHistory.xlsx
+++ b/StructureDefinition-SEEHDSLMMedicationHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
